--- a/summary_stats/chuuchuu_summary_2025_12.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_12.xlsx
@@ -1533,25 +1533,25 @@
         <v>98</v>
       </c>
       <c r="N14" t="n">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="O14" t="n">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="P14" t="n">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="Q14" t="n">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="R14" t="n">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="S14" t="n">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="T14" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="U14" t="n">
         <v>1594</v>
@@ -1691,25 +1691,25 @@
         <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O16" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P16" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R16" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>127</v>
@@ -1849,25 +1849,25 @@
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O18" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P18" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q18" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R18" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U18" t="n">
         <v>362</v>
@@ -1928,25 +1928,25 @@
         <v>725</v>
       </c>
       <c r="N19" t="n">
-        <v>2424</v>
+        <v>2166</v>
       </c>
       <c r="O19" t="n">
-        <v>2079</v>
+        <v>1845</v>
       </c>
       <c r="P19" t="n">
-        <v>1949</v>
+        <v>1725</v>
       </c>
       <c r="Q19" t="n">
-        <v>1523</v>
+        <v>1328</v>
       </c>
       <c r="R19" t="n">
-        <v>1210</v>
+        <v>1042</v>
       </c>
       <c r="S19" t="n">
-        <v>550</v>
+        <v>435</v>
       </c>
       <c r="T19" t="n">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="U19" t="n">
         <v>3990</v>
@@ -2007,25 +2007,25 @@
         <v>60</v>
       </c>
       <c r="N20" t="n">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="O20" t="n">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="P20" t="n">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="Q20" t="n">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="R20" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="S20" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="T20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U20" t="n">
         <v>1410</v>
@@ -2086,25 +2086,25 @@
         <v>1673</v>
       </c>
       <c r="N21" t="n">
-        <v>8901</v>
+        <v>8272</v>
       </c>
       <c r="O21" t="n">
-        <v>7712</v>
+        <v>7126</v>
       </c>
       <c r="P21" t="n">
-        <v>7224</v>
+        <v>6656</v>
       </c>
       <c r="Q21" t="n">
-        <v>5781</v>
+        <v>5267</v>
       </c>
       <c r="R21" t="n">
-        <v>4471</v>
+        <v>4026</v>
       </c>
       <c r="S21" t="n">
-        <v>2137</v>
+        <v>1864</v>
       </c>
       <c r="T21" t="n">
-        <v>591</v>
+        <v>475</v>
       </c>
       <c r="U21" t="n">
         <v>15158</v>
@@ -2165,25 +2165,25 @@
         <v>223</v>
       </c>
       <c r="N22" t="n">
-        <v>2606</v>
+        <v>2513</v>
       </c>
       <c r="O22" t="n">
-        <v>2276</v>
+        <v>2188</v>
       </c>
       <c r="P22" t="n">
-        <v>2145</v>
+        <v>2059</v>
       </c>
       <c r="Q22" t="n">
-        <v>1720</v>
+        <v>1640</v>
       </c>
       <c r="R22" t="n">
-        <v>1354</v>
+        <v>1287</v>
       </c>
       <c r="S22" t="n">
-        <v>637</v>
+        <v>587</v>
       </c>
       <c r="T22" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="U22" t="n">
         <v>4030</v>
@@ -2481,25 +2481,25 @@
         <v>36</v>
       </c>
       <c r="N26" t="n">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="O26" t="n">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="P26" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="Q26" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="R26" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="S26" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U26" t="n">
         <v>660</v>
@@ -2560,22 +2560,22 @@
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2639,25 +2639,25 @@
         <v>39</v>
       </c>
       <c r="N28" t="n">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="O28" t="n">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="P28" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="Q28" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="R28" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="S28" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="T28" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U28" t="n">
         <v>770</v>
@@ -3350,25 +3350,25 @@
         <v>397</v>
       </c>
       <c r="N37" t="n">
-        <v>1004</v>
+        <v>936</v>
       </c>
       <c r="O37" t="n">
-        <v>990</v>
+        <v>925</v>
       </c>
       <c r="P37" t="n">
-        <v>984</v>
+        <v>921</v>
       </c>
       <c r="Q37" t="n">
-        <v>736</v>
+        <v>693</v>
       </c>
       <c r="R37" t="n">
-        <v>588</v>
+        <v>552</v>
       </c>
       <c r="S37" t="n">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="T37" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="U37" t="n">
         <v>3342</v>
@@ -3429,25 +3429,25 @@
         <v>35</v>
       </c>
       <c r="N38" t="n">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="O38" t="n">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="P38" t="n">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="Q38" t="n">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="R38" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="S38" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="T38" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="U38" t="n">
         <v>424</v>
@@ -3508,25 +3508,25 @@
         <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O39" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P39" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R39" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
         <v>65</v>
@@ -4298,13 +4298,13 @@
         <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O49" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q49" t="n">
         <v>22</v>
@@ -4377,22 +4377,22 @@
         <v>2527</v>
       </c>
       <c r="N50" t="n">
-        <v>4175</v>
+        <v>4074</v>
       </c>
       <c r="O50" t="n">
-        <v>2318</v>
+        <v>2255</v>
       </c>
       <c r="P50" t="n">
-        <v>1805</v>
+        <v>1754</v>
       </c>
       <c r="Q50" t="n">
-        <v>872</v>
+        <v>838</v>
       </c>
       <c r="R50" t="n">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="S50" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>684</v>
       </c>
       <c r="N52" t="n">
-        <v>511</v>
+        <v>456</v>
       </c>
       <c r="O52" t="n">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="P52" t="n">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="Q52" t="n">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="R52" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -4614,25 +4614,25 @@
         <v>41</v>
       </c>
       <c r="N53" t="n">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="O53" t="n">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="P53" t="n">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="Q53" t="n">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="R53" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="S53" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="T53" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="U53" t="n">
         <v>890</v>
@@ -4851,19 +4851,19 @@
         <v>161</v>
       </c>
       <c r="N56" t="n">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="O56" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="P56" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="Q56" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="R56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -4930,19 +4930,19 @@
         <v>2403</v>
       </c>
       <c r="N57" t="n">
-        <v>5381</v>
+        <v>5282</v>
       </c>
       <c r="O57" t="n">
-        <v>2417</v>
+        <v>2354</v>
       </c>
       <c r="P57" t="n">
-        <v>1753</v>
+        <v>1706</v>
       </c>
       <c r="Q57" t="n">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="R57" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="S57" t="n">
         <v>16</v>
@@ -5009,19 +5009,19 @@
         <v>952</v>
       </c>
       <c r="N58" t="n">
-        <v>2444</v>
+        <v>2401</v>
       </c>
       <c r="O58" t="n">
-        <v>949</v>
+        <v>923</v>
       </c>
       <c r="P58" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="Q58" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="R58" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S58" t="n">
         <v>9</v>
@@ -5325,16 +5325,16 @@
         <v>13</v>
       </c>
       <c r="N62" t="n">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O62" t="n">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P62" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q62" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R62" t="n">
         <v>204</v>
@@ -5483,19 +5483,19 @@
         <v>62</v>
       </c>
       <c r="N64" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="O64" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="P64" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Q64" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="R64" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S64" t="n">
         <v>40</v>
@@ -5799,25 +5799,25 @@
         <v>11</v>
       </c>
       <c r="N68" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O68" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P68" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q68" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R68" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U68" t="n">
         <v>1754</v>
@@ -6115,25 +6115,25 @@
         <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="O72" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P72" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="Q72" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="R72" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="S72" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U72" t="n">
         <v>1368</v>
@@ -6352,25 +6352,25 @@
         <v>28</v>
       </c>
       <c r="N75" t="n">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="O75" t="n">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="P75" t="n">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="Q75" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="R75" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="S75" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U75" t="n">
         <v>1042</v>
@@ -6431,22 +6431,22 @@
         <v>11</v>
       </c>
       <c r="N76" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O76" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P76" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q76" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R76" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S76" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T76" t="n">
         <v>22</v>
@@ -6668,25 +6668,25 @@
         <v>8</v>
       </c>
       <c r="N79" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O79" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P79" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q79" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R79" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S79" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U79" t="n">
         <v>311</v>
@@ -7616,22 +7616,22 @@
         <v>54</v>
       </c>
       <c r="N91" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="O91" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P91" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q91" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R91" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="S91" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T91" t="n">
         <v>19</v>
@@ -8248,22 +8248,22 @@
         <v>213</v>
       </c>
       <c r="N99" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O99" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P99" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q99" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R99" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T99" t="n">
         <v>5</v>
@@ -9117,19 +9117,19 @@
         <v>13</v>
       </c>
       <c r="N110" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="O110" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P110" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="Q110" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="R110" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="S110" t="n">
         <v>9</v>
@@ -9196,22 +9196,22 @@
         <v>464</v>
       </c>
       <c r="N111" t="n">
-        <v>4744</v>
+        <v>4696</v>
       </c>
       <c r="O111" t="n">
-        <v>2786</v>
+        <v>2749</v>
       </c>
       <c r="P111" t="n">
-        <v>2228</v>
+        <v>2196</v>
       </c>
       <c r="Q111" t="n">
-        <v>1135</v>
+        <v>1111</v>
       </c>
       <c r="R111" t="n">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="S111" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="T111" t="n">
         <v>7</v>
@@ -9275,19 +9275,19 @@
         <v>56</v>
       </c>
       <c r="N112" t="n">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="O112" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="P112" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q112" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="R112" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S112" t="n">
         <v>13</v>
@@ -9433,22 +9433,22 @@
         <v>32</v>
       </c>
       <c r="N114" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O114" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P114" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q114" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R114" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S114" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T114" t="n">
         <v>7</v>
@@ -9512,19 +9512,19 @@
         <v>115</v>
       </c>
       <c r="N115" t="n">
-        <v>2290</v>
+        <v>2281</v>
       </c>
       <c r="O115" t="n">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="P115" t="n">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="Q115" t="n">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="R115" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S115" t="n">
         <v>34</v>
@@ -9828,22 +9828,22 @@
         <v>46</v>
       </c>
       <c r="N119" t="n">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="O119" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="P119" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q119" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R119" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S119" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T119" t="n">
         <v>0</v>
@@ -9986,22 +9986,22 @@
         <v>251</v>
       </c>
       <c r="N121" t="n">
-        <v>3310</v>
+        <v>3285</v>
       </c>
       <c r="O121" t="n">
-        <v>1802</v>
+        <v>1784</v>
       </c>
       <c r="P121" t="n">
-        <v>1422</v>
+        <v>1404</v>
       </c>
       <c r="Q121" t="n">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="R121" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="S121" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T121" t="n">
         <v>5</v>
@@ -10065,19 +10065,19 @@
         <v>93</v>
       </c>
       <c r="N122" t="n">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="O122" t="n">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="P122" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="Q122" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R122" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>
@@ -10618,7 +10618,7 @@
         <v>38</v>
       </c>
       <c r="N129" t="n">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="O129" t="n">
         <v>363</v>
@@ -10934,25 +10934,25 @@
         <v>16</v>
       </c>
       <c r="N133" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O133" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P133" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q133" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R133" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S133" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T133" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U133" t="n">
         <v>333</v>
@@ -11250,25 +11250,25 @@
         <v>8</v>
       </c>
       <c r="N137" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O137" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P137" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q137" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="R137" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="S137" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T137" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U137" t="n">
         <v>663</v>
@@ -12672,22 +12672,22 @@
         <v>26</v>
       </c>
       <c r="N155" t="n">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="O155" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="P155" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="Q155" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="R155" t="n">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="S155" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T155" t="n">
         <v>48</v>
@@ -12751,7 +12751,7 @@
         <v>1</v>
       </c>
       <c r="N156" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O156" t="n">
         <v>56</v>
@@ -12909,25 +12909,25 @@
         <v>1283</v>
       </c>
       <c r="N158" t="n">
-        <v>5928</v>
+        <v>5798</v>
       </c>
       <c r="O158" t="n">
-        <v>2857</v>
+        <v>2770</v>
       </c>
       <c r="P158" t="n">
-        <v>2850</v>
+        <v>2763</v>
       </c>
       <c r="Q158" t="n">
-        <v>1912</v>
+        <v>1846</v>
       </c>
       <c r="R158" t="n">
-        <v>1357</v>
+        <v>1305</v>
       </c>
       <c r="S158" t="n">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="T158" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="U158" t="n">
         <v>35270</v>
@@ -12988,25 +12988,25 @@
         <v>134</v>
       </c>
       <c r="N159" t="n">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="O159" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="P159" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Q159" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="R159" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="S159" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U159" t="n">
         <v>4970</v>
@@ -13146,25 +13146,25 @@
         <v>3</v>
       </c>
       <c r="N161" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O161" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P161" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q161" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R161" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
         <v>98</v>
@@ -14805,25 +14805,25 @@
         <v>33</v>
       </c>
       <c r="N182" t="n">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="O182" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P182" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q182" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R182" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S182" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T182" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U182" t="n">
         <v>1467</v>
@@ -15200,25 +15200,25 @@
         <v>8</v>
       </c>
       <c r="N187" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O187" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P187" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q187" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R187" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S187" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T187" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U187" t="n">
         <v>505</v>
@@ -15358,25 +15358,25 @@
         <v>66</v>
       </c>
       <c r="N189" t="n">
-        <v>3447</v>
+        <v>3424</v>
       </c>
       <c r="O189" t="n">
-        <v>2764</v>
+        <v>2744</v>
       </c>
       <c r="P189" t="n">
-        <v>2499</v>
+        <v>2479</v>
       </c>
       <c r="Q189" t="n">
-        <v>1803</v>
+        <v>1784</v>
       </c>
       <c r="R189" t="n">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="S189" t="n">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="T189" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="U189" t="n">
         <v>6851</v>
@@ -15437,25 +15437,25 @@
         <v>110</v>
       </c>
       <c r="N190" t="n">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="O190" t="n">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="P190" t="n">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="Q190" t="n">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="R190" t="n">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="S190" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="T190" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U190" t="n">
         <v>3150</v>
@@ -15595,22 +15595,22 @@
         <v>4</v>
       </c>
       <c r="N192" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T192" t="n">
         <v>0</v>
@@ -15753,19 +15753,19 @@
         <v>166</v>
       </c>
       <c r="N194" t="n">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="O194" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P194" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="Q194" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R194" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S194" t="n">
         <v>24</v>
@@ -16069,25 +16069,25 @@
         <v>5</v>
       </c>
       <c r="N198" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O198" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P198" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q198" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="R198" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S198" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T198" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U198" t="n">
         <v>242</v>
@@ -16148,25 +16148,25 @@
         <v>7875</v>
       </c>
       <c r="N199" t="n">
-        <v>45116</v>
+        <v>44645</v>
       </c>
       <c r="O199" t="n">
-        <v>25386</v>
+        <v>25040</v>
       </c>
       <c r="P199" t="n">
-        <v>19845</v>
+        <v>19544</v>
       </c>
       <c r="Q199" t="n">
-        <v>9733</v>
+        <v>9531</v>
       </c>
       <c r="R199" t="n">
-        <v>5498</v>
+        <v>5351</v>
       </c>
       <c r="S199" t="n">
-        <v>1773</v>
+        <v>1724</v>
       </c>
       <c r="T199" t="n">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="U199" t="n">
         <v>221477</v>
@@ -16227,16 +16227,16 @@
         <v>264</v>
       </c>
       <c r="N200" t="n">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="O200" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="P200" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q200" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R200" t="n">
         <v>62</v>
@@ -17017,22 +17017,22 @@
         <v>2</v>
       </c>
       <c r="N210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R210" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T210" t="n">
         <v>0</v>
@@ -18115,22 +18115,22 @@
         <v>23</v>
       </c>
       <c r="N224" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="O224" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="P224" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="Q224" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="R224" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S224" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T224" t="n">
         <v>1</v>
@@ -18641,25 +18641,25 @@
         <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P2" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="Q2" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="T2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V2" t="n">
         <v>663</v>
@@ -18809,25 +18809,25 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97</v>
@@ -19985,7 +19985,7 @@
         <v>38</v>
       </c>
       <c r="O18" t="n">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="P18" t="n">
         <v>363</v>
@@ -20237,25 +20237,25 @@
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R21" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V21" t="n">
         <v>333</v>
@@ -21581,22 +21581,22 @@
         <v>26</v>
       </c>
       <c r="O37" t="n">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="P37" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="Q37" t="n">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="R37" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="S37" t="n">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="T37" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="U37" t="n">
         <v>48</v>
@@ -21665,7 +21665,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P38" t="n">
         <v>54</v>
@@ -21833,25 +21833,25 @@
         <v>1283</v>
       </c>
       <c r="O40" t="n">
-        <v>5928</v>
+        <v>5798</v>
       </c>
       <c r="P40" t="n">
-        <v>2857</v>
+        <v>2770</v>
       </c>
       <c r="Q40" t="n">
-        <v>2850</v>
+        <v>2763</v>
       </c>
       <c r="R40" t="n">
-        <v>1912</v>
+        <v>1846</v>
       </c>
       <c r="S40" t="n">
-        <v>1357</v>
+        <v>1305</v>
       </c>
       <c r="T40" t="n">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="U40" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="V40" t="n">
         <v>35270</v>
@@ -21917,25 +21917,25 @@
         <v>133</v>
       </c>
       <c r="O41" t="n">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="P41" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q41" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="R41" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="S41" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="T41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>4643</v>
@@ -23471,25 +23471,25 @@
         <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="T3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V3" t="n">
         <v>233</v>
@@ -23639,25 +23639,25 @@
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>43</v>
@@ -23723,25 +23723,25 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>36</v>
@@ -23891,19 +23891,19 @@
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
         <v>4</v>
@@ -23975,19 +23975,19 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
         <v>6</v>
@@ -24143,25 +24143,25 @@
         <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="P11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="T11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>89</v>
@@ -24311,25 +24311,25 @@
         <v>725</v>
       </c>
       <c r="O13" t="n">
-        <v>2416</v>
+        <v>2158</v>
       </c>
       <c r="P13" t="n">
-        <v>2073</v>
+        <v>1839</v>
       </c>
       <c r="Q13" t="n">
-        <v>1944</v>
+        <v>1720</v>
       </c>
       <c r="R13" t="n">
-        <v>1521</v>
+        <v>1326</v>
       </c>
       <c r="S13" t="n">
-        <v>1209</v>
+        <v>1041</v>
       </c>
       <c r="T13" t="n">
-        <v>550</v>
+        <v>435</v>
       </c>
       <c r="U13" t="n">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="V13" t="n">
         <v>3980</v>
@@ -24395,19 +24395,19 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T14" t="n">
         <v>7</v>
@@ -24479,25 +24479,25 @@
         <v>1673</v>
       </c>
       <c r="O15" t="n">
-        <v>8901</v>
+        <v>8272</v>
       </c>
       <c r="P15" t="n">
-        <v>7712</v>
+        <v>7126</v>
       </c>
       <c r="Q15" t="n">
-        <v>7224</v>
+        <v>6656</v>
       </c>
       <c r="R15" t="n">
-        <v>5781</v>
+        <v>5267</v>
       </c>
       <c r="S15" t="n">
-        <v>4471</v>
+        <v>4026</v>
       </c>
       <c r="T15" t="n">
-        <v>2137</v>
+        <v>1864</v>
       </c>
       <c r="U15" t="n">
-        <v>591</v>
+        <v>475</v>
       </c>
       <c r="V15" t="n">
         <v>15158</v>
@@ -24647,22 +24647,22 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -24731,25 +24731,25 @@
         <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="P18" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R18" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S18" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V18" t="n">
         <v>293</v>
@@ -24983,22 +24983,22 @@
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -25319,25 +25319,25 @@
         <v>45</v>
       </c>
       <c r="O25" t="n">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="P25" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="Q25" t="n">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="R25" t="n">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="S25" t="n">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="T25" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="U25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="V25" t="n">
         <v>879</v>
@@ -25403,25 +25403,25 @@
         <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P26" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R26" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="S26" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>128</v>
@@ -25487,22 +25487,22 @@
         <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R27" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U27" t="n">
         <v>4</v>
@@ -25571,25 +25571,25 @@
         <v>51</v>
       </c>
       <c r="O28" t="n">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="P28" t="n">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="Q28" t="n">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="R28" t="n">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="S28" t="n">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="T28" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="U28" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="V28" t="n">
         <v>814</v>
@@ -25655,25 +25655,25 @@
         <v>17</v>
       </c>
       <c r="O29" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="P29" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="Q29" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R29" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="S29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="T29" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
         <v>268</v>
@@ -25907,13 +25907,13 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R32" t="n">
         <v>21</v>
@@ -25991,22 +25991,22 @@
         <v>15</v>
       </c>
       <c r="O33" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P33" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q33" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S33" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -26075,25 +26075,25 @@
         <v>26</v>
       </c>
       <c r="O34" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="P34" t="n">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Q34" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R34" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="S34" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="U34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V34" t="n">
         <v>718</v>
@@ -26159,25 +26159,25 @@
         <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q35" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="R35" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S35" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="T35" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="U35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V35" t="n">
         <v>52</v>
@@ -26327,25 +26327,25 @@
         <v>23</v>
       </c>
       <c r="O37" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="P37" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="Q37" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="R37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="S37" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T37" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="U37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V37" t="n">
         <v>234</v>
@@ -26411,25 +26411,25 @@
         <v>84</v>
       </c>
       <c r="O38" t="n">
-        <v>760</v>
+        <v>723</v>
       </c>
       <c r="P38" t="n">
-        <v>662</v>
+        <v>626</v>
       </c>
       <c r="Q38" t="n">
-        <v>624</v>
+        <v>588</v>
       </c>
       <c r="R38" t="n">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="S38" t="n">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="T38" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="U38" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V38" t="n">
         <v>1353</v>
@@ -26579,25 +26579,25 @@
         <v>30</v>
       </c>
       <c r="O40" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="P40" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="Q40" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="R40" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="S40" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="T40" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V40" t="n">
         <v>450</v>
@@ -26663,25 +26663,25 @@
         <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="P41" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Q41" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="R41" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S41" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T41" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U41" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V41" t="n">
         <v>534</v>
@@ -27251,25 +27251,25 @@
         <v>36</v>
       </c>
       <c r="O48" t="n">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="P48" t="n">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="Q48" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="R48" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="S48" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="T48" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="U48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="V48" t="n">
         <v>657</v>
@@ -27587,19 +27587,19 @@
         <v>28</v>
       </c>
       <c r="O52" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="P52" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="Q52" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R52" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="S52" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T52" t="n">
         <v>27</v>
@@ -28133,25 +28133,25 @@
         <v>41</v>
       </c>
       <c r="O3" t="n">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="P3" t="n">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="n">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="R3" t="n">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="S3" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="T3" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="V3" t="n">
         <v>890</v>
@@ -28301,22 +28301,22 @@
         <v>2527</v>
       </c>
       <c r="O5" t="n">
-        <v>4175</v>
+        <v>4074</v>
       </c>
       <c r="P5" t="n">
-        <v>2318</v>
+        <v>2255</v>
       </c>
       <c r="Q5" t="n">
-        <v>1805</v>
+        <v>1754</v>
       </c>
       <c r="R5" t="n">
-        <v>872</v>
+        <v>838</v>
       </c>
       <c r="S5" t="n">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="T5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -28385,22 +28385,22 @@
         <v>684</v>
       </c>
       <c r="O6" t="n">
-        <v>511</v>
+        <v>456</v>
       </c>
       <c r="P6" t="n">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="Q6" t="n">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="S6" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="T6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -28553,19 +28553,19 @@
         <v>161</v>
       </c>
       <c r="O8" t="n">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="Q8" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -28637,19 +28637,19 @@
         <v>2403</v>
       </c>
       <c r="O9" t="n">
-        <v>5381</v>
+        <v>5282</v>
       </c>
       <c r="P9" t="n">
-        <v>2417</v>
+        <v>2354</v>
       </c>
       <c r="Q9" t="n">
-        <v>1753</v>
+        <v>1706</v>
       </c>
       <c r="R9" t="n">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="S9" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="T9" t="n">
         <v>16</v>
@@ -28721,19 +28721,19 @@
         <v>952</v>
       </c>
       <c r="O10" t="n">
-        <v>2444</v>
+        <v>2401</v>
       </c>
       <c r="P10" t="n">
-        <v>949</v>
+        <v>923</v>
       </c>
       <c r="Q10" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="R10" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="S10" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="T10" t="n">
         <v>9</v>
@@ -28805,13 +28805,13 @@
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R11" t="n">
         <v>22</v>
@@ -30275,16 +30275,16 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
@@ -32207,19 +32207,19 @@
         <v>62</v>
       </c>
       <c r="O39" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="P39" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Q39" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="R39" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="S39" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T39" t="n">
         <v>40</v>
@@ -32459,25 +32459,25 @@
         <v>11</v>
       </c>
       <c r="O42" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P42" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q42" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R42" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42" t="n">
         <v>1754</v>
@@ -32795,25 +32795,25 @@
         <v>60</v>
       </c>
       <c r="O46" t="n">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="P46" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="Q46" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="R46" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="S46" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="T46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
         <v>1368</v>
@@ -33047,25 +33047,25 @@
         <v>28</v>
       </c>
       <c r="O49" t="n">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="P49" t="n">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="Q49" t="n">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="R49" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="S49" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="T49" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="U49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V49" t="n">
         <v>1042</v>
@@ -33131,22 +33131,22 @@
         <v>11</v>
       </c>
       <c r="O50" t="n">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P50" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q50" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="R50" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S50" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T50" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U50" t="n">
         <v>19</v>
@@ -34769,22 +34769,22 @@
         <v>213</v>
       </c>
       <c r="O10" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P10" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R10" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U10" t="n">
         <v>5</v>
@@ -36617,22 +36617,22 @@
         <v>34</v>
       </c>
       <c r="O32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
         <v>3</v>
@@ -36995,22 +36995,22 @@
         <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P2" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Q2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="R2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="S2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U2" t="n">
         <v>7</v>
@@ -37079,19 +37079,19 @@
         <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="P3" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="R3" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="T3" t="n">
         <v>9</v>
@@ -37247,22 +37247,22 @@
         <v>464</v>
       </c>
       <c r="O5" t="n">
-        <v>4744</v>
+        <v>4696</v>
       </c>
       <c r="P5" t="n">
-        <v>2786</v>
+        <v>2749</v>
       </c>
       <c r="Q5" t="n">
-        <v>2228</v>
+        <v>2196</v>
       </c>
       <c r="R5" t="n">
-        <v>1135</v>
+        <v>1111</v>
       </c>
       <c r="S5" t="n">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="T5" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="U5" t="n">
         <v>7</v>
@@ -37331,19 +37331,19 @@
         <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="P6" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="Q6" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="R6" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T6" t="n">
         <v>11</v>
@@ -37499,19 +37499,19 @@
         <v>115</v>
       </c>
       <c r="O8" t="n">
-        <v>2290</v>
+        <v>2281</v>
       </c>
       <c r="P8" t="n">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="Q8" t="n">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="R8" t="n">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="S8" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="T8" t="n">
         <v>34</v>
@@ -37667,22 +37667,22 @@
         <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="P10" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="Q10" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="R10" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -37835,22 +37835,22 @@
         <v>251</v>
       </c>
       <c r="O12" t="n">
-        <v>3310</v>
+        <v>3285</v>
       </c>
       <c r="P12" t="n">
-        <v>1802</v>
+        <v>1784</v>
       </c>
       <c r="Q12" t="n">
-        <v>1422</v>
+        <v>1404</v>
       </c>
       <c r="R12" t="n">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="S12" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="T12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U12" t="n">
         <v>5</v>
@@ -37919,19 +37919,19 @@
         <v>92</v>
       </c>
       <c r="O13" t="n">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="P13" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="Q13" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="R13" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T13" t="n">
         <v>20</v>
@@ -38003,7 +38003,7 @@
         <v>28</v>
       </c>
       <c r="O14" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P14" t="n">
         <v>86</v>
@@ -38087,13 +38087,13 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>5</v>
@@ -38717,25 +38717,25 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>268</v>
@@ -39137,25 +39137,25 @@
         <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="T8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V8" t="n">
         <v>241</v>
@@ -39809,7 +39809,7 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P16" t="n">
         <v>274</v>
@@ -40313,25 +40313,25 @@
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P22" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Q22" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R22" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S22" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T22" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>505</v>
@@ -40481,25 +40481,25 @@
         <v>66</v>
       </c>
       <c r="O24" t="n">
-        <v>3447</v>
+        <v>3424</v>
       </c>
       <c r="P24" t="n">
-        <v>2764</v>
+        <v>2744</v>
       </c>
       <c r="Q24" t="n">
-        <v>2499</v>
+        <v>2479</v>
       </c>
       <c r="R24" t="n">
-        <v>1803</v>
+        <v>1784</v>
       </c>
       <c r="S24" t="n">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="T24" t="n">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="U24" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="V24" t="n">
         <v>6851</v>
@@ -40565,25 +40565,25 @@
         <v>110</v>
       </c>
       <c r="O25" t="n">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="P25" t="n">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="Q25" t="n">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="R25" t="n">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="S25" t="n">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="T25" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="U25" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="V25" t="n">
         <v>3150</v>
@@ -40733,22 +40733,22 @@
         <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -40817,19 +40817,19 @@
         <v>166</v>
       </c>
       <c r="O28" t="n">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="P28" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q28" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="R28" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T28" t="n">
         <v>24</v>
@@ -41069,25 +41069,25 @@
         <v>7875</v>
       </c>
       <c r="O31" t="n">
-        <v>45116</v>
+        <v>44645</v>
       </c>
       <c r="P31" t="n">
-        <v>25386</v>
+        <v>25040</v>
       </c>
       <c r="Q31" t="n">
-        <v>19845</v>
+        <v>19544</v>
       </c>
       <c r="R31" t="n">
-        <v>9733</v>
+        <v>9531</v>
       </c>
       <c r="S31" t="n">
-        <v>5498</v>
+        <v>5351</v>
       </c>
       <c r="T31" t="n">
-        <v>1773</v>
+        <v>1724</v>
       </c>
       <c r="U31" t="n">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="V31" t="n">
         <v>221477</v>
@@ -41153,16 +41153,16 @@
         <v>264</v>
       </c>
       <c r="O32" t="n">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="P32" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="Q32" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="R32" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S32" t="n">
         <v>62</v>

--- a/summary_stats/chuuchuu_summary_2025_12.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_12.xlsx
@@ -18109,10 +18109,10 @@
         <v>1</v>
       </c>
       <c r="L224" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M224" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N224" t="n">
         <v>159</v>
